--- a/public/FYN93N_ATO_Logbook.xlsx
+++ b/public/FYN93N_ATO_Logbook.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P67"/>
+  <dimension ref="A1:P107"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -481,7 +481,7 @@
         <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K2" t="str">
-        <v>Visit Parramatta HQ before IKEA Marsden Park trip</v>
+        <v>Regular Visit to HQ meeting (Toll-Free route via Great Western Hwy)</v>
       </c>
       <c r="L2">
         <v>38.61</v>
@@ -510,7 +510,7 @@
         <v>Completed</v>
       </c>
       <c r="D3" t="str">
-        <v>01/05/2026</v>
+        <v>03/05/2026</v>
       </c>
       <c r="E3" t="str">
         <v>FYN93N</v>
@@ -519,22 +519,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G3">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="H3">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="I3" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J3" t="str">
-        <v>Ikea Marsden Park, Hollinsworth, Marsden Park NSW, Australia</v>
+        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
       </c>
       <c r="K3" t="str">
-        <v>Travel from Parramatta HQ to IKEA Marsden Park</v>
+        <v>Buying books</v>
       </c>
       <c r="L3">
-        <v>22.62</v>
+        <v>30.79</v>
       </c>
       <c r="M3">
         <v>1</v>
@@ -543,7 +543,7 @@
         <v>Yes</v>
       </c>
       <c r="O3">
-        <v>45.24</v>
+        <v>61.58</v>
       </c>
       <c r="P3" t="str">
         <v>Y</v>
@@ -560,7 +560,7 @@
         <v>Completed</v>
       </c>
       <c r="D4" t="str">
-        <v>01/05/2026</v>
+        <v>04/05/2026</v>
       </c>
       <c r="E4" t="str">
         <v>FYN93N</v>
@@ -569,22 +569,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G4">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="H4">
-        <v>298</v>
+        <v>343</v>
       </c>
       <c r="I4" t="str">
-        <v>Ikea Marsden Park, Hollinsworth, Marsden Park NSW, Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J4" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K4" t="str">
-        <v>Return from IKEA Marsden Park to Penrith</v>
+        <v>Regular Visit to HQ</v>
       </c>
       <c r="L4">
-        <v>22.62</v>
+        <v>38.61</v>
       </c>
       <c r="M4">
         <v>1</v>
@@ -593,7 +593,7 @@
         <v>Yes</v>
       </c>
       <c r="O4">
-        <v>45.24</v>
+        <v>77.22</v>
       </c>
       <c r="P4" t="str">
         <v>Y</v>
@@ -610,7 +610,7 @@
         <v>Completed</v>
       </c>
       <c r="D5" t="str">
-        <v>03/05/2026</v>
+        <v>10/05/2026</v>
       </c>
       <c r="E5" t="str">
         <v>FYN93N</v>
@@ -619,10 +619,10 @@
         <v>Employee - work</v>
       </c>
       <c r="G5">
-        <v>298</v>
+        <v>347</v>
       </c>
       <c r="H5">
-        <v>360</v>
+        <v>409</v>
       </c>
       <c r="I5" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
@@ -646,7 +646,7 @@
         <v>61.58</v>
       </c>
       <c r="P5" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
         <v>Completed</v>
       </c>
       <c r="D6" t="str">
-        <v>04/05/2026</v>
+        <v>11/05/2026</v>
       </c>
       <c r="E6" t="str">
         <v>FYN93N</v>
@@ -669,10 +669,10 @@
         <v>Employee - work</v>
       </c>
       <c r="G6">
-        <v>360</v>
+        <v>415</v>
       </c>
       <c r="H6">
-        <v>437</v>
+        <v>492</v>
       </c>
       <c r="I6" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
@@ -696,7 +696,7 @@
         <v>77.22</v>
       </c>
       <c r="P6" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="7">
@@ -710,7 +710,7 @@
         <v>Completed</v>
       </c>
       <c r="D7" t="str">
-        <v>10/05/2026</v>
+        <v>12/05/2026</v>
       </c>
       <c r="E7" t="str">
         <v>FYN93N</v>
@@ -719,34 +719,34 @@
         <v>Employee - work</v>
       </c>
       <c r="G7">
-        <v>437</v>
+        <v>492</v>
       </c>
       <c r="H7">
-        <v>498</v>
+        <v>530</v>
       </c>
       <c r="I7" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J7" t="str">
-        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K7" t="str">
-        <v>Buying books</v>
+        <v>Attended Parramatta HQ meeting (Leg 1/3)</v>
       </c>
       <c r="L7">
-        <v>30.79</v>
+        <v>38.61</v>
       </c>
       <c r="M7">
         <v>1</v>
       </c>
       <c r="N7" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O7">
-        <v>61.58</v>
+        <v>38.61</v>
       </c>
       <c r="P7" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="8">
@@ -760,7 +760,7 @@
         <v>Completed</v>
       </c>
       <c r="D8" t="str">
-        <v>11/05/2026</v>
+        <v>12/05/2026</v>
       </c>
       <c r="E8" t="str">
         <v>FYN93N</v>
@@ -769,34 +769,34 @@
         <v>Employee - work</v>
       </c>
       <c r="G8">
-        <v>498</v>
+        <v>530</v>
       </c>
       <c r="H8">
-        <v>653</v>
+        <v>553</v>
       </c>
       <c r="I8" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="J8" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Costco Wholesale Marsden Park, Richmond Road, Marsden Park NSW Australia</v>
       </c>
       <c r="K8" t="str">
-        <v>Regular Visit to HQ</v>
+        <v>Travel from Parramatta HQ to Costco Marsden Park for bulk supplies (Leg 2/3)</v>
       </c>
       <c r="L8">
-        <v>38.61</v>
+        <v>22.2</v>
       </c>
       <c r="M8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N8" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O8">
-        <v>154.44</v>
+        <v>22.2</v>
       </c>
       <c r="P8" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="9">
@@ -810,7 +810,7 @@
         <v>Completed</v>
       </c>
       <c r="D9" t="str">
-        <v>17/05/2026</v>
+        <v>12/05/2026</v>
       </c>
       <c r="E9" t="str">
         <v>FYN93N</v>
@@ -819,34 +819,34 @@
         <v>Employee - work</v>
       </c>
       <c r="G9">
-        <v>653</v>
+        <v>553</v>
       </c>
       <c r="H9">
-        <v>714</v>
+        <v>581</v>
       </c>
       <c r="I9" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>Costco Wholesale Marsden Park, Richmond Road, Marsden Park NSW Australia</v>
       </c>
       <c r="J9" t="str">
-        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="K9" t="str">
-        <v>Buying books</v>
+        <v>Return from Costco Marsden Park to Penrith (Leg 3/3)</v>
       </c>
       <c r="L9">
-        <v>30.79</v>
+        <v>27.88</v>
       </c>
       <c r="M9">
         <v>1</v>
       </c>
       <c r="N9" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O9">
-        <v>61.58</v>
+        <v>27.88</v>
       </c>
       <c r="P9" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="10">
@@ -860,7 +860,7 @@
         <v>Completed</v>
       </c>
       <c r="D10" t="str">
-        <v>18/05/2026</v>
+        <v>17/05/2026</v>
       </c>
       <c r="E10" t="str">
         <v>FYN93N</v>
@@ -869,22 +869,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G10">
-        <v>714</v>
+        <v>591</v>
       </c>
       <c r="H10">
-        <v>792</v>
+        <v>652</v>
       </c>
       <c r="I10" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J10" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
       </c>
       <c r="K10" t="str">
-        <v>Regular Visit to HQ</v>
+        <v>Buying books</v>
       </c>
       <c r="L10">
-        <v>38.61</v>
+        <v>30.79</v>
       </c>
       <c r="M10">
         <v>1</v>
@@ -893,10 +893,10 @@
         <v>Yes</v>
       </c>
       <c r="O10">
-        <v>77.22</v>
+        <v>61.58</v>
       </c>
       <c r="P10" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="11">
@@ -910,7 +910,7 @@
         <v>Completed</v>
       </c>
       <c r="D11" t="str">
-        <v>23/05/2026</v>
+        <v>18/05/2026</v>
       </c>
       <c r="E11" t="str">
         <v>FYN93N</v>
@@ -919,10 +919,10 @@
         <v>Employee - work</v>
       </c>
       <c r="G11">
-        <v>298</v>
+        <v>652</v>
       </c>
       <c r="H11">
-        <v>375</v>
+        <v>730</v>
       </c>
       <c r="I11" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
@@ -931,7 +931,7 @@
         <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K11" t="str">
-        <v>Visit Parramatta HQ before Lidcombe shopping trip</v>
+        <v>Regular Visit to HQ</v>
       </c>
       <c r="L11">
         <v>38.61</v>
@@ -960,7 +960,7 @@
         <v>Completed</v>
       </c>
       <c r="D12" t="str">
-        <v>23/05/2026</v>
+        <v>20/05/2026</v>
       </c>
       <c r="E12" t="str">
         <v>FYN93N</v>
@@ -969,22 +969,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G12">
-        <v>389</v>
+        <v>738</v>
       </c>
       <c r="H12">
-        <v>468</v>
+        <v>815</v>
       </c>
       <c r="I12" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J12" t="str">
-        <v>KMall09 Lidcombe Shopping Centre, Parramatta Road, Lidcombe NSW, Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K12" t="str">
-        <v>Travel from Parramatta HQ to KMall09 Lidcombe</v>
+        <v>Regular Visit to HQ meeting (Toll-Free route via Great Western Hwy)</v>
       </c>
       <c r="L12">
-        <v>39.4</v>
+        <v>38.61</v>
       </c>
       <c r="M12">
         <v>1</v>
@@ -993,7 +993,7 @@
         <v>Yes</v>
       </c>
       <c r="O12">
-        <v>78.8</v>
+        <v>77.22</v>
       </c>
       <c r="P12" t="str">
         <v>Y</v>
@@ -1010,7 +1010,7 @@
         <v>Completed</v>
       </c>
       <c r="D13" t="str">
-        <v>23/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="E13" t="str">
         <v>FYN93N</v>
@@ -1019,31 +1019,31 @@
         <v>Employee - work</v>
       </c>
       <c r="G13">
-        <v>475</v>
+        <v>827</v>
       </c>
       <c r="H13">
-        <v>554</v>
+        <v>866</v>
       </c>
       <c r="I13" t="str">
-        <v>KMall09 Lidcombe Shopping Centre, Parramatta Road, Lidcombe NSW, Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J13" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K13" t="str">
-        <v>Return from KMall09 Lidcombe to Penrith</v>
+        <v>Attended Parramatta HQ meeting (Leg 1/3)</v>
       </c>
       <c r="L13">
-        <v>39.4</v>
+        <v>38.61</v>
       </c>
       <c r="M13">
         <v>1</v>
       </c>
       <c r="N13" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O13">
-        <v>78.8</v>
+        <v>38.61</v>
       </c>
       <c r="P13" t="str">
         <v>Y</v>
@@ -1060,7 +1060,7 @@
         <v>Completed</v>
       </c>
       <c r="D14" t="str">
-        <v>24/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="E14" t="str">
         <v>FYN93N</v>
@@ -1069,34 +1069,34 @@
         <v>Employee - work</v>
       </c>
       <c r="G14">
-        <v>792</v>
+        <v>866</v>
       </c>
       <c r="H14">
-        <v>853</v>
+        <v>888</v>
       </c>
       <c r="I14" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="J14" t="str">
-        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+        <v>Costco Wholesale Marsden Park, Richmond Road, Marsden Park NSW Australia</v>
       </c>
       <c r="K14" t="str">
-        <v>Buying books</v>
+        <v>Travel from Parramatta HQ to Costco Marsden Park for bulk supplies (Leg 2/3)</v>
       </c>
       <c r="L14">
-        <v>30.79</v>
+        <v>22.2</v>
       </c>
       <c r="M14">
         <v>1</v>
       </c>
       <c r="N14" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O14">
-        <v>61.58</v>
+        <v>22.2</v>
       </c>
       <c r="P14" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="15">
@@ -1110,7 +1110,7 @@
         <v>Completed</v>
       </c>
       <c r="D15" t="str">
-        <v>25/05/2026</v>
+        <v>22/05/2026</v>
       </c>
       <c r="E15" t="str">
         <v>FYN93N</v>
@@ -1119,34 +1119,34 @@
         <v>Employee - work</v>
       </c>
       <c r="G15">
-        <v>853</v>
+        <v>888</v>
       </c>
       <c r="H15">
-        <v>1008</v>
+        <v>916</v>
       </c>
       <c r="I15" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>Costco Wholesale Marsden Park, Richmond Road, Marsden Park NSW Australia</v>
       </c>
       <c r="J15" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="K15" t="str">
-        <v>Regular Visit to HQ</v>
+        <v>Return from Costco Marsden Park to Penrith (Leg 3/3)</v>
       </c>
       <c r="L15">
-        <v>38.61</v>
+        <v>27.88</v>
       </c>
       <c r="M15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N15" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O15">
-        <v>154.44</v>
+        <v>27.88</v>
       </c>
       <c r="P15" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="16">
@@ -1160,7 +1160,7 @@
         <v>Completed</v>
       </c>
       <c r="D16" t="str">
-        <v>28/05/2026</v>
+        <v>24/05/2026</v>
       </c>
       <c r="E16" t="str">
         <v>FYN93N</v>
@@ -1169,10 +1169,10 @@
         <v>Employee - work</v>
       </c>
       <c r="G16">
-        <v>565</v>
+        <v>927</v>
       </c>
       <c r="H16">
-        <v>626</v>
+        <v>988</v>
       </c>
       <c r="I16" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
@@ -1181,7 +1181,7 @@
         <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
       </c>
       <c r="K16" t="str">
-        <v>Visit Five Senses Education before reporting to HQ</v>
+        <v>Buying books</v>
       </c>
       <c r="L16">
         <v>30.79</v>
@@ -1210,7 +1210,7 @@
         <v>Completed</v>
       </c>
       <c r="D17" t="str">
-        <v>28/05/2026</v>
+        <v>25/05/2026</v>
       </c>
       <c r="E17" t="str">
         <v>FYN93N</v>
@@ -1219,19 +1219,19 @@
         <v>Employee - work</v>
       </c>
       <c r="G17">
-        <v>626</v>
+        <v>999</v>
       </c>
       <c r="H17">
-        <v>703</v>
+        <v>1076</v>
       </c>
       <c r="I17" t="str">
-        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J17" t="str">
         <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K17" t="str">
-        <v>Travel from Seven Hills to Parramatta HQ</v>
+        <v>Regular Visit to HQ</v>
       </c>
       <c r="L17">
         <v>38.61</v>
@@ -1260,7 +1260,7 @@
         <v>Completed</v>
       </c>
       <c r="D18" t="str">
-        <v>28/05/2026</v>
+        <v>27/05/2026</v>
       </c>
       <c r="E18" t="str">
         <v>FYN93N</v>
@@ -1269,22 +1269,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G18">
-        <v>712</v>
+        <v>1076</v>
       </c>
       <c r="H18">
-        <v>789</v>
+        <v>1150</v>
       </c>
       <c r="I18" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J18" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K18" t="str">
-        <v>Return from Parramatta HQ to Penrith</v>
+        <v>Urgent executive meeting at HQ (via M4 Motorway)</v>
       </c>
       <c r="L18">
-        <v>38.61</v>
+        <v>36.8</v>
       </c>
       <c r="M18">
         <v>1</v>
@@ -1293,7 +1293,7 @@
         <v>Yes</v>
       </c>
       <c r="O18">
-        <v>77.22</v>
+        <v>73.6</v>
       </c>
       <c r="P18" t="str">
         <v>Y</v>
@@ -1310,7 +1310,7 @@
         <v>Completed</v>
       </c>
       <c r="D19" t="str">
-        <v>30/05/2026</v>
+        <v>29/05/2026</v>
       </c>
       <c r="E19" t="str">
         <v>FYN93N</v>
@@ -1319,34 +1319,34 @@
         <v>Employee - work</v>
       </c>
       <c r="G19">
-        <v>1008</v>
+        <v>1155</v>
       </c>
       <c r="H19">
-        <v>1069</v>
+        <v>1194</v>
       </c>
       <c r="I19" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J19" t="str">
-        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K19" t="str">
-        <v>Buying books</v>
+        <v>Attended Parramatta HQ meeting (Leg 1/3)</v>
       </c>
       <c r="L19">
-        <v>30.79</v>
+        <v>38.61</v>
       </c>
       <c r="M19">
         <v>1</v>
       </c>
       <c r="N19" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O19">
-        <v>61.58</v>
+        <v>38.61</v>
       </c>
       <c r="P19" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="20">
@@ -1360,7 +1360,7 @@
         <v>Completed</v>
       </c>
       <c r="D20" t="str">
-        <v>31/05/2026</v>
+        <v>29/05/2026</v>
       </c>
       <c r="E20" t="str">
         <v>FYN93N</v>
@@ -1369,31 +1369,31 @@
         <v>Employee - work</v>
       </c>
       <c r="G20">
-        <v>793</v>
+        <v>1194</v>
       </c>
       <c r="H20">
-        <v>854</v>
+        <v>1204</v>
       </c>
       <c r="I20" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="J20" t="str">
-        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+        <v>KMall09 Lidcombe Shopping Centre, Parramatta Road, Lidcombe NSW, Australia</v>
       </c>
       <c r="K20" t="str">
-        <v>Buying books</v>
+        <v>Travel from Parramatta HQ to KMall09 Lidcombe for educational supplies (Leg 2/3)</v>
       </c>
       <c r="L20">
-        <v>30.79</v>
+        <v>10.82</v>
       </c>
       <c r="M20">
         <v>1</v>
       </c>
       <c r="N20" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O20">
-        <v>61.58</v>
+        <v>10.82</v>
       </c>
       <c r="P20" t="str">
         <v>Y</v>
@@ -1410,7 +1410,7 @@
         <v>Completed</v>
       </c>
       <c r="D21" t="str">
-        <v>01/06/2026</v>
+        <v>29/05/2026</v>
       </c>
       <c r="E21" t="str">
         <v>FYN93N</v>
@@ -1419,34 +1419,34 @@
         <v>Employee - work</v>
       </c>
       <c r="G21">
-        <v>1069</v>
+        <v>1204</v>
       </c>
       <c r="H21">
-        <v>1224</v>
+        <v>1243</v>
       </c>
       <c r="I21" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>KMall09 Lidcombe Shopping Centre, Parramatta Road, Lidcombe NSW, Australia</v>
       </c>
       <c r="J21" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="K21" t="str">
-        <v>Regular Visit to HQ</v>
+        <v>Return from KMall09 Lidcombe to Penrith (Leg 3/3)</v>
       </c>
       <c r="L21">
-        <v>38.61</v>
+        <v>38.66</v>
       </c>
       <c r="M21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N21" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O21">
-        <v>154.44</v>
+        <v>38.66</v>
       </c>
       <c r="P21" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="22">
@@ -1460,7 +1460,7 @@
         <v>Completed</v>
       </c>
       <c r="D22" t="str">
-        <v>06/06/2026</v>
+        <v>31/05/2026</v>
       </c>
       <c r="E22" t="str">
         <v>FYN93N</v>
@@ -1469,22 +1469,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G22">
-        <v>864</v>
+        <v>1243</v>
       </c>
       <c r="H22">
-        <v>941</v>
+        <v>1305</v>
       </c>
       <c r="I22" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J22" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
       </c>
       <c r="K22" t="str">
-        <v>Visit Parramatta HQ before Costco stop</v>
+        <v>Buying books</v>
       </c>
       <c r="L22">
-        <v>38.61</v>
+        <v>30.79</v>
       </c>
       <c r="M22">
         <v>1</v>
@@ -1493,7 +1493,7 @@
         <v>Yes</v>
       </c>
       <c r="O22">
-        <v>77.22</v>
+        <v>61.58</v>
       </c>
       <c r="P22" t="str">
         <v>Y</v>
@@ -1510,7 +1510,7 @@
         <v>Completed</v>
       </c>
       <c r="D23" t="str">
-        <v>06/06/2026</v>
+        <v>01/06/2026</v>
       </c>
       <c r="E23" t="str">
         <v>FYN93N</v>
@@ -1519,22 +1519,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G23">
-        <v>950</v>
+        <v>1305</v>
       </c>
       <c r="H23">
-        <v>1029</v>
+        <v>1382</v>
       </c>
       <c r="I23" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J23" t="str">
-        <v>Costco Wholesale Marsden Park, Richmond Road, Marsden Park NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K23" t="str">
-        <v>Travel from Parramatta HQ to Costco Marsden Park</v>
+        <v>Regular Visit to HQ</v>
       </c>
       <c r="L23">
-        <v>39.5</v>
+        <v>38.61</v>
       </c>
       <c r="M23">
         <v>1</v>
@@ -1543,7 +1543,7 @@
         <v>Yes</v>
       </c>
       <c r="O23">
-        <v>79</v>
+        <v>77.22</v>
       </c>
       <c r="P23" t="str">
         <v>Y</v>
@@ -1560,7 +1560,7 @@
         <v>Completed</v>
       </c>
       <c r="D24" t="str">
-        <v>06/06/2026</v>
+        <v>07/06/2026</v>
       </c>
       <c r="E24" t="str">
         <v>FYN93N</v>
@@ -1569,22 +1569,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G24">
-        <v>1044</v>
+        <v>1382</v>
       </c>
       <c r="H24">
-        <v>1123</v>
+        <v>1443</v>
       </c>
       <c r="I24" t="str">
-        <v>Costco Wholesale Marsden Park, Richmond Road, Marsden Park NSW Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J24" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
       </c>
       <c r="K24" t="str">
-        <v>Return from Costco Marsden Park to Penrith</v>
+        <v>Buying books</v>
       </c>
       <c r="L24">
-        <v>39.5</v>
+        <v>30.79</v>
       </c>
       <c r="M24">
         <v>1</v>
@@ -1593,7 +1593,7 @@
         <v>Yes</v>
       </c>
       <c r="O24">
-        <v>79</v>
+        <v>61.58</v>
       </c>
       <c r="P24" t="str">
         <v>Y</v>
@@ -1610,7 +1610,7 @@
         <v>Completed</v>
       </c>
       <c r="D25" t="str">
-        <v>07/06/2026</v>
+        <v>13/06/2026</v>
       </c>
       <c r="E25" t="str">
         <v>FYN93N</v>
@@ -1619,22 +1619,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G25">
-        <v>1224</v>
+        <v>1443</v>
       </c>
       <c r="H25">
-        <v>1285</v>
+        <v>1500</v>
       </c>
       <c r="I25" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J25" t="str">
-        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+        <v>Ikea Marsden Park, Hollinsworth, Marsden Park NSW, Australia</v>
       </c>
       <c r="K25" t="str">
-        <v>Buying books</v>
+        <v>Purchase office furniture and fixtures (Toll-Free via Richmond Rd)</v>
       </c>
       <c r="L25">
-        <v>30.79</v>
+        <v>28.3</v>
       </c>
       <c r="M25">
         <v>1</v>
@@ -1643,10 +1643,10 @@
         <v>Yes</v>
       </c>
       <c r="O25">
-        <v>61.58</v>
+        <v>56.6</v>
       </c>
       <c r="P25" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="26">
@@ -1660,7 +1660,7 @@
         <v>Completed</v>
       </c>
       <c r="D26" t="str">
-        <v>08/06/2026</v>
+        <v>14/06/2026</v>
       </c>
       <c r="E26" t="str">
         <v>FYN93N</v>
@@ -1669,22 +1669,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G26">
-        <v>1285</v>
+        <v>1506</v>
       </c>
       <c r="H26">
-        <v>1362</v>
+        <v>1568</v>
       </c>
       <c r="I26" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J26" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
       </c>
       <c r="K26" t="str">
-        <v>Regular Visit to HQ</v>
+        <v>Buying books</v>
       </c>
       <c r="L26">
-        <v>38.61</v>
+        <v>30.79</v>
       </c>
       <c r="M26">
         <v>1</v>
@@ -1693,10 +1693,10 @@
         <v>Yes</v>
       </c>
       <c r="O26">
-        <v>77.22</v>
+        <v>61.58</v>
       </c>
       <c r="P26" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="27">
@@ -1710,7 +1710,7 @@
         <v>Completed</v>
       </c>
       <c r="D27" t="str">
-        <v>14/06/2026</v>
+        <v>15/06/2026</v>
       </c>
       <c r="E27" t="str">
         <v>FYN93N</v>
@@ -1719,22 +1719,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G27">
-        <v>1362</v>
+        <v>1568</v>
       </c>
       <c r="H27">
-        <v>1424</v>
+        <v>1645</v>
       </c>
       <c r="I27" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J27" t="str">
-        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K27" t="str">
-        <v>Buying books</v>
+        <v>Regular Visit to HQ</v>
       </c>
       <c r="L27">
-        <v>30.79</v>
+        <v>38.61</v>
       </c>
       <c r="M27">
         <v>1</v>
@@ -1743,10 +1743,10 @@
         <v>Yes</v>
       </c>
       <c r="O27">
-        <v>61.58</v>
+        <v>77.22</v>
       </c>
       <c r="P27" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="28">
@@ -1760,7 +1760,7 @@
         <v>Completed</v>
       </c>
       <c r="D28" t="str">
-        <v>15/06/2026</v>
+        <v>18/06/2026</v>
       </c>
       <c r="E28" t="str">
         <v>FYN93N</v>
@@ -1769,10 +1769,10 @@
         <v>Employee - work</v>
       </c>
       <c r="G28">
-        <v>1126</v>
+        <v>1653</v>
       </c>
       <c r="H28">
-        <v>1204</v>
+        <v>1692</v>
       </c>
       <c r="I28" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
@@ -1781,7 +1781,7 @@
         <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K28" t="str">
-        <v>Regular Visit to HQ</v>
+        <v>Attended Parramatta HQ meeting (Leg 1/3)</v>
       </c>
       <c r="L28">
         <v>38.61</v>
@@ -1790,10 +1790,10 @@
         <v>1</v>
       </c>
       <c r="N28" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O28">
-        <v>77.22</v>
+        <v>38.61</v>
       </c>
       <c r="P28" t="str">
         <v>Y</v>
@@ -1819,31 +1819,31 @@
         <v>Employee - work</v>
       </c>
       <c r="G29">
-        <v>1204</v>
+        <v>1692</v>
       </c>
       <c r="H29">
-        <v>1281</v>
+        <v>1714</v>
       </c>
       <c r="I29" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="J29" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Costco Wholesale Marsden Park, Richmond Road, Marsden Park NSW Australia</v>
       </c>
       <c r="K29" t="str">
-        <v>Visit Parramatta HQ before Lidcombe shopping trip</v>
+        <v>Travel from Parramatta HQ to Costco Marsden Park for bulk supplies (Leg 2/3)</v>
       </c>
       <c r="L29">
-        <v>38.61</v>
+        <v>22.2</v>
       </c>
       <c r="M29">
         <v>1</v>
       </c>
       <c r="N29" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O29">
-        <v>77.22</v>
+        <v>22.2</v>
       </c>
       <c r="P29" t="str">
         <v>Y</v>
@@ -1869,31 +1869,31 @@
         <v>Employee - work</v>
       </c>
       <c r="G30">
-        <v>1281</v>
+        <v>1714</v>
       </c>
       <c r="H30">
-        <v>1360</v>
+        <v>1742</v>
       </c>
       <c r="I30" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Costco Wholesale Marsden Park, Richmond Road, Marsden Park NSW Australia</v>
       </c>
       <c r="J30" t="str">
-        <v>KMall09 Lidcombe Shopping Centre, Parramatta Road, Lidcombe NSW, Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="K30" t="str">
-        <v>Travel from Parramatta HQ to KMall09 Lidcombe</v>
+        <v>Return from Costco Marsden Park to Penrith (Leg 3/3)</v>
       </c>
       <c r="L30">
-        <v>39.4</v>
+        <v>27.88</v>
       </c>
       <c r="M30">
         <v>1</v>
       </c>
       <c r="N30" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O30">
-        <v>78.8</v>
+        <v>27.88</v>
       </c>
       <c r="P30" t="str">
         <v>Y</v>
@@ -1910,7 +1910,7 @@
         <v>Completed</v>
       </c>
       <c r="D31" t="str">
-        <v>18/06/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="E31" t="str">
         <v>FYN93N</v>
@@ -1919,31 +1919,31 @@
         <v>Employee - work</v>
       </c>
       <c r="G31">
-        <v>1365</v>
+        <v>1742</v>
       </c>
       <c r="H31">
-        <v>1444</v>
+        <v>1781</v>
       </c>
       <c r="I31" t="str">
-        <v>KMall09 Lidcombe Shopping Centre, Parramatta Road, Lidcombe NSW, Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J31" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K31" t="str">
-        <v>Return from KMall09 Lidcombe to Penrith</v>
+        <v>Attended Parramatta HQ meeting (Leg 1/3)</v>
       </c>
       <c r="L31">
-        <v>39.4</v>
+        <v>38.61</v>
       </c>
       <c r="M31">
         <v>1</v>
       </c>
       <c r="N31" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O31">
-        <v>78.8</v>
+        <v>38.61</v>
       </c>
       <c r="P31" t="str">
         <v>Y</v>
@@ -1960,7 +1960,7 @@
         <v>Completed</v>
       </c>
       <c r="D32" t="str">
-        <v>21/06/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="E32" t="str">
         <v>FYN93N</v>
@@ -1969,34 +1969,34 @@
         <v>Employee - work</v>
       </c>
       <c r="G32">
-        <v>1444</v>
+        <v>1781</v>
       </c>
       <c r="H32">
-        <v>1676</v>
+        <v>1803</v>
       </c>
       <c r="I32" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="J32" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Costco Wholesale Marsden Park, Richmond Road, Marsden Park NSW Australia</v>
       </c>
       <c r="K32" t="str">
-        <v>Regular Visit to HQ</v>
+        <v>Travel from Parramatta HQ to Costco Marsden Park for bulk supplies (Leg 2/3)</v>
       </c>
       <c r="L32">
-        <v>38.61</v>
+        <v>22.2</v>
       </c>
       <c r="M32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N32" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O32">
-        <v>231.66</v>
+        <v>22.2</v>
       </c>
       <c r="P32" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="33">
@@ -2010,7 +2010,7 @@
         <v>Completed</v>
       </c>
       <c r="D33" t="str">
-        <v>22/06/2026</v>
+        <v>19/06/2026</v>
       </c>
       <c r="E33" t="str">
         <v>FYN93N</v>
@@ -2019,34 +2019,34 @@
         <v>Employee - work</v>
       </c>
       <c r="G33">
-        <v>1676</v>
+        <v>1803</v>
       </c>
       <c r="H33">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="I33" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>Costco Wholesale Marsden Park, Richmond Road, Marsden Park NSW Australia</v>
       </c>
       <c r="J33" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="K33" t="str">
-        <v>Regular Visit to HQ</v>
+        <v>Return from Costco Marsden Park to Penrith (Leg 3/3)</v>
       </c>
       <c r="L33">
-        <v>38.61</v>
+        <v>27.88</v>
       </c>
       <c r="M33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N33" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O33">
-        <v>154.44</v>
+        <v>27.88</v>
       </c>
       <c r="P33" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="34">
@@ -2060,7 +2060,7 @@
         <v>Completed</v>
       </c>
       <c r="D34" t="str">
-        <v>23/06/2026</v>
+        <v>21/06/2026</v>
       </c>
       <c r="E34" t="str">
         <v>FYN93N</v>
@@ -2069,22 +2069,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G34">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="H34">
-        <v>1907</v>
+        <v>1892</v>
       </c>
       <c r="I34" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J34" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
       </c>
       <c r="K34" t="str">
-        <v>Regular Visit to HQ meeting</v>
+        <v>Buying books</v>
       </c>
       <c r="L34">
-        <v>38.61</v>
+        <v>30.79</v>
       </c>
       <c r="M34">
         <v>1</v>
@@ -2093,10 +2093,10 @@
         <v>Yes</v>
       </c>
       <c r="O34">
-        <v>77.22</v>
+        <v>61.58</v>
       </c>
       <c r="P34" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="35">
@@ -2110,7 +2110,7 @@
         <v>Completed</v>
       </c>
       <c r="D35" t="str">
-        <v>24/06/2026</v>
+        <v>22/06/2026</v>
       </c>
       <c r="E35" t="str">
         <v>FYN93N</v>
@@ -2119,22 +2119,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G35">
-        <v>1454</v>
+        <v>1892</v>
       </c>
       <c r="H35">
-        <v>1515</v>
+        <v>1970</v>
       </c>
       <c r="I35" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J35" t="str">
-        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K35" t="str">
-        <v>Visit Five Senses Education before reporting to HQ</v>
+        <v>Regular Visit to HQ</v>
       </c>
       <c r="L35">
-        <v>30.79</v>
+        <v>38.61</v>
       </c>
       <c r="M35">
         <v>1</v>
@@ -2143,7 +2143,7 @@
         <v>Yes</v>
       </c>
       <c r="O35">
-        <v>61.58</v>
+        <v>77.22</v>
       </c>
       <c r="P35" t="str">
         <v>Y</v>
@@ -2160,7 +2160,7 @@
         <v>Completed</v>
       </c>
       <c r="D36" t="str">
-        <v>24/06/2026</v>
+        <v>26/06/2026</v>
       </c>
       <c r="E36" t="str">
         <v>FYN93N</v>
@@ -2169,19 +2169,19 @@
         <v>Employee - work</v>
       </c>
       <c r="G36">
-        <v>1530</v>
+        <v>1976</v>
       </c>
       <c r="H36">
-        <v>1607</v>
+        <v>2014</v>
       </c>
       <c r="I36" t="str">
-        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J36" t="str">
         <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K36" t="str">
-        <v>Travel from Seven Hills to Parramatta HQ</v>
+        <v>Attended Parramatta HQ meeting (Leg 1/3)</v>
       </c>
       <c r="L36">
         <v>38.61</v>
@@ -2190,10 +2190,10 @@
         <v>1</v>
       </c>
       <c r="N36" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O36">
-        <v>77.22</v>
+        <v>38.61</v>
       </c>
       <c r="P36" t="str">
         <v>Y</v>
@@ -2210,7 +2210,7 @@
         <v>Completed</v>
       </c>
       <c r="D37" t="str">
-        <v>24/06/2026</v>
+        <v>26/06/2026</v>
       </c>
       <c r="E37" t="str">
         <v>FYN93N</v>
@@ -2219,31 +2219,31 @@
         <v>Employee - work</v>
       </c>
       <c r="G37">
-        <v>1614</v>
+        <v>2014</v>
       </c>
       <c r="H37">
-        <v>1692</v>
+        <v>2025</v>
       </c>
       <c r="I37" t="str">
         <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="J37" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>KMall09 Lidcombe Shopping Centre, Parramatta Road, Lidcombe NSW, Australia</v>
       </c>
       <c r="K37" t="str">
-        <v>Return from Parramatta HQ to Penrith</v>
+        <v>Travel from Parramatta HQ to KMall09 Lidcombe for educational supplies (Leg 2/3)</v>
       </c>
       <c r="L37">
-        <v>38.61</v>
+        <v>10.82</v>
       </c>
       <c r="M37">
         <v>1</v>
       </c>
       <c r="N37" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O37">
-        <v>77.22</v>
+        <v>10.82</v>
       </c>
       <c r="P37" t="str">
         <v>Y</v>
@@ -2260,7 +2260,7 @@
         <v>Completed</v>
       </c>
       <c r="D38" t="str">
-        <v>28/06/2026</v>
+        <v>26/06/2026</v>
       </c>
       <c r="E38" t="str">
         <v>FYN93N</v>
@@ -2269,34 +2269,34 @@
         <v>Employee - work</v>
       </c>
       <c r="G38">
-        <v>1907</v>
+        <v>2025</v>
       </c>
       <c r="H38">
-        <v>1969</v>
+        <v>2064</v>
       </c>
       <c r="I38" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>KMall09 Lidcombe Shopping Centre, Parramatta Road, Lidcombe NSW, Australia</v>
       </c>
       <c r="J38" t="str">
-        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="K38" t="str">
-        <v>Buying books</v>
+        <v>Return from KMall09 Lidcombe to Penrith (Leg 3/3)</v>
       </c>
       <c r="L38">
-        <v>30.79</v>
+        <v>38.66</v>
       </c>
       <c r="M38">
         <v>1</v>
       </c>
       <c r="N38" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O38">
-        <v>61.58</v>
+        <v>38.66</v>
       </c>
       <c r="P38" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="39">
@@ -2310,7 +2310,7 @@
         <v>Completed</v>
       </c>
       <c r="D39" t="str">
-        <v>29/06/2026</v>
+        <v>27/06/2026</v>
       </c>
       <c r="E39" t="str">
         <v>FYN93N</v>
@@ -2319,22 +2319,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G39">
-        <v>1969</v>
+        <v>2073</v>
       </c>
       <c r="H39">
-        <v>2046</v>
+        <v>2155</v>
       </c>
       <c r="I39" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J39" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>KMall09 Lidcombe Shopping Centre, Parramatta Road, Lidcombe NSW, Australia</v>
       </c>
       <c r="K39" t="str">
-        <v>Regular Visit to HQ</v>
+        <v>Purchase Korean educational &amp; office supplies (Toll-Free route)</v>
       </c>
       <c r="L39">
-        <v>38.61</v>
+        <v>40.75</v>
       </c>
       <c r="M39">
         <v>1</v>
@@ -2343,10 +2343,10 @@
         <v>Yes</v>
       </c>
       <c r="O39">
-        <v>77.22</v>
+        <v>81.5</v>
       </c>
       <c r="P39" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="40">
@@ -2360,7 +2360,7 @@
         <v>Completed</v>
       </c>
       <c r="D40" t="str">
-        <v>01/07/2026</v>
+        <v>28/06/2026</v>
       </c>
       <c r="E40" t="str">
         <v>FYN93N</v>
@@ -2369,22 +2369,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G40">
-        <v>2046</v>
+        <v>2155</v>
       </c>
       <c r="H40">
-        <v>2123</v>
+        <v>2216</v>
       </c>
       <c r="I40" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J40" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
       </c>
       <c r="K40" t="str">
-        <v>Regular Visit to HQ meeting</v>
+        <v>Buying books</v>
       </c>
       <c r="L40">
-        <v>38.61</v>
+        <v>30.79</v>
       </c>
       <c r="M40">
         <v>1</v>
@@ -2393,10 +2393,10 @@
         <v>Yes</v>
       </c>
       <c r="O40">
-        <v>77.22</v>
+        <v>61.58</v>
       </c>
       <c r="P40" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="41">
@@ -2410,7 +2410,7 @@
         <v>Completed</v>
       </c>
       <c r="D41" t="str">
-        <v>05/07/2026</v>
+        <v>29/06/2026</v>
       </c>
       <c r="E41" t="str">
         <v>FYN93N</v>
@@ -2419,22 +2419,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G41">
-        <v>2123</v>
+        <v>2216</v>
       </c>
       <c r="H41">
-        <v>2185</v>
+        <v>2293</v>
       </c>
       <c r="I41" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J41" t="str">
-        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K41" t="str">
-        <v>Buying books</v>
+        <v>Regular Visit to HQ</v>
       </c>
       <c r="L41">
-        <v>30.79</v>
+        <v>38.61</v>
       </c>
       <c r="M41">
         <v>1</v>
@@ -2443,10 +2443,10 @@
         <v>Yes</v>
       </c>
       <c r="O41">
-        <v>61.58</v>
+        <v>77.22</v>
       </c>
       <c r="P41" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="42">
@@ -2460,7 +2460,7 @@
         <v>Completed</v>
       </c>
       <c r="D42" t="str">
-        <v>06/07/2026</v>
+        <v>02/07/2026</v>
       </c>
       <c r="E42" t="str">
         <v>FYN93N</v>
@@ -2469,10 +2469,10 @@
         <v>Employee - work</v>
       </c>
       <c r="G42">
-        <v>2185</v>
+        <v>2293</v>
       </c>
       <c r="H42">
-        <v>2262</v>
+        <v>2332</v>
       </c>
       <c r="I42" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
@@ -2481,7 +2481,7 @@
         <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K42" t="str">
-        <v>Regular Visit to HQ</v>
+        <v>Attended Parramatta HQ meeting (Leg 1/3)</v>
       </c>
       <c r="L42">
         <v>38.61</v>
@@ -2490,13 +2490,13 @@
         <v>1</v>
       </c>
       <c r="N42" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O42">
-        <v>77.22</v>
+        <v>38.61</v>
       </c>
       <c r="P42" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="43">
@@ -2510,7 +2510,7 @@
         <v>Completed</v>
       </c>
       <c r="D43" t="str">
-        <v>09/07/2026</v>
+        <v>02/07/2026</v>
       </c>
       <c r="E43" t="str">
         <v>FYN93N</v>
@@ -2519,34 +2519,34 @@
         <v>Employee - work</v>
       </c>
       <c r="G43">
-        <v>2262</v>
+        <v>2332</v>
       </c>
       <c r="H43">
-        <v>2417</v>
+        <v>2343</v>
       </c>
       <c r="I43" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="J43" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>KMall09 Lidcombe Shopping Centre, Parramatta Road, Lidcombe NSW, Australia</v>
       </c>
       <c r="K43" t="str">
-        <v>Regular Visit to HQ meeting</v>
+        <v>Travel from Parramatta HQ to KMall09 Lidcombe for educational supplies (Leg 2/3)</v>
       </c>
       <c r="L43">
-        <v>38.61</v>
+        <v>10.82</v>
       </c>
       <c r="M43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N43" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O43">
-        <v>154.44</v>
+        <v>10.82</v>
       </c>
       <c r="P43" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="44">
@@ -2560,7 +2560,7 @@
         <v>Completed</v>
       </c>
       <c r="D44" t="str">
-        <v>12/07/2026</v>
+        <v>02/07/2026</v>
       </c>
       <c r="E44" t="str">
         <v>FYN93N</v>
@@ -2569,34 +2569,34 @@
         <v>Employee - work</v>
       </c>
       <c r="G44">
-        <v>2417</v>
+        <v>2343</v>
       </c>
       <c r="H44">
-        <v>2478</v>
+        <v>2382</v>
       </c>
       <c r="I44" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>KMall09 Lidcombe Shopping Centre, Parramatta Road, Lidcombe NSW, Australia</v>
       </c>
       <c r="J44" t="str">
-        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="K44" t="str">
-        <v>Buying books</v>
+        <v>Return from KMall09 Lidcombe to Penrith (Leg 3/3)</v>
       </c>
       <c r="L44">
-        <v>30.79</v>
+        <v>38.66</v>
       </c>
       <c r="M44">
         <v>1</v>
       </c>
       <c r="N44" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O44">
-        <v>61.58</v>
+        <v>38.66</v>
       </c>
       <c r="P44" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="45">
@@ -2610,7 +2610,7 @@
         <v>Completed</v>
       </c>
       <c r="D45" t="str">
-        <v>13/07/2026</v>
+        <v>03/07/2026</v>
       </c>
       <c r="E45" t="str">
         <v>FYN93N</v>
@@ -2619,22 +2619,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G45">
-        <v>2478</v>
+        <v>2393</v>
       </c>
       <c r="H45">
-        <v>2555</v>
+        <v>2474</v>
       </c>
       <c r="I45" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J45" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>KMall09 Lidcombe Shopping Centre, Parramatta Road, Lidcombe NSW, Australia</v>
       </c>
       <c r="K45" t="str">
-        <v>Regular Visit to HQ</v>
+        <v>Purchase Korean educational &amp; office supplies (Toll-Free route)</v>
       </c>
       <c r="L45">
-        <v>38.61</v>
+        <v>40.75</v>
       </c>
       <c r="M45">
         <v>1</v>
@@ -2643,10 +2643,10 @@
         <v>Yes</v>
       </c>
       <c r="O45">
-        <v>77.22</v>
+        <v>81.5</v>
       </c>
       <c r="P45" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="46">
@@ -2660,7 +2660,7 @@
         <v>Completed</v>
       </c>
       <c r="D46" t="str">
-        <v>14/07/2026</v>
+        <v>05/07/2026</v>
       </c>
       <c r="E46" t="str">
         <v>FYN93N</v>
@@ -2669,22 +2669,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G46">
-        <v>2555</v>
+        <v>2479</v>
       </c>
       <c r="H46">
-        <v>2633</v>
+        <v>2540</v>
       </c>
       <c r="I46" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J46" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
       </c>
       <c r="K46" t="str">
-        <v>Regular Visit to HQ pick up</v>
+        <v>Buying books</v>
       </c>
       <c r="L46">
-        <v>38.61</v>
+        <v>30.79</v>
       </c>
       <c r="M46">
         <v>1</v>
@@ -2693,10 +2693,10 @@
         <v>Yes</v>
       </c>
       <c r="O46">
-        <v>77.22</v>
+        <v>61.58</v>
       </c>
       <c r="P46" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="47">
@@ -2710,7 +2710,7 @@
         <v>Completed</v>
       </c>
       <c r="D47" t="str">
-        <v>14/07/2026</v>
+        <v>06/07/2026</v>
       </c>
       <c r="E47" t="str">
         <v>FYN93N</v>
@@ -2719,22 +2719,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G47">
-        <v>2633</v>
+        <v>2544</v>
       </c>
       <c r="H47">
-        <v>2694</v>
+        <v>2622</v>
       </c>
       <c r="I47" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J47" t="str">
-        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K47" t="str">
-        <v>Buying books</v>
+        <v>Regular Visit to HQ</v>
       </c>
       <c r="L47">
-        <v>30.79</v>
+        <v>38.61</v>
       </c>
       <c r="M47">
         <v>1</v>
@@ -2743,10 +2743,10 @@
         <v>Yes</v>
       </c>
       <c r="O47">
-        <v>61.58</v>
+        <v>77.22</v>
       </c>
       <c r="P47" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="48">
@@ -2760,7 +2760,7 @@
         <v>Completed</v>
       </c>
       <c r="D48" t="str">
-        <v>16/07/2026</v>
+        <v>07/07/2026</v>
       </c>
       <c r="E48" t="str">
         <v>FYN93N</v>
@@ -2769,22 +2769,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G48">
-        <v>2694</v>
+        <v>2630</v>
       </c>
       <c r="H48">
-        <v>2771</v>
+        <v>2686</v>
       </c>
       <c r="I48" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J48" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Ikea Marsden Park, Hollinsworth, Marsden Park NSW, Australia</v>
       </c>
       <c r="K48" t="str">
-        <v>Regular Visit to HQ meeting</v>
+        <v>Purchase office furniture and fixtures (Toll-Free via Richmond Rd)</v>
       </c>
       <c r="L48">
-        <v>38.61</v>
+        <v>28.3</v>
       </c>
       <c r="M48">
         <v>1</v>
@@ -2793,10 +2793,10 @@
         <v>Yes</v>
       </c>
       <c r="O48">
-        <v>77.22</v>
+        <v>56.6</v>
       </c>
       <c r="P48" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="49">
@@ -2810,7 +2810,7 @@
         <v>Completed</v>
       </c>
       <c r="D49" t="str">
-        <v>19/07/2026</v>
+        <v>09/07/2026</v>
       </c>
       <c r="E49" t="str">
         <v>FYN93N</v>
@@ -2819,10 +2819,10 @@
         <v>Employee - work</v>
       </c>
       <c r="G49">
-        <v>2771</v>
+        <v>2691</v>
       </c>
       <c r="H49">
-        <v>2926</v>
+        <v>2768</v>
       </c>
       <c r="I49" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
@@ -2831,22 +2831,22 @@
         <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K49" t="str">
-        <v>Regular Visit to HQ</v>
+        <v>Regular Visit to HQ meeting (Toll-Free route via Great Western Hwy)</v>
       </c>
       <c r="L49">
         <v>38.61</v>
       </c>
       <c r="M49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N49" t="str">
         <v>Yes</v>
       </c>
       <c r="O49">
-        <v>154.44</v>
+        <v>77.22</v>
       </c>
       <c r="P49" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="50">
@@ -2860,7 +2860,7 @@
         <v>Completed</v>
       </c>
       <c r="D50" t="str">
-        <v>20/07/2026</v>
+        <v>10/07/2026</v>
       </c>
       <c r="E50" t="str">
         <v>FYN93N</v>
@@ -2869,22 +2869,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G50">
-        <v>1692</v>
+        <v>2773</v>
       </c>
       <c r="H50">
-        <v>1769</v>
+        <v>2829</v>
       </c>
       <c r="I50" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J50" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Ikea Marsden Park, Hollinsworth, Marsden Park NSW, Australia</v>
       </c>
       <c r="K50" t="str">
-        <v>Regular Visit to HQ</v>
+        <v>Purchase office furniture and fixtures (Toll-Free via Richmond Rd)</v>
       </c>
       <c r="L50">
-        <v>38.61</v>
+        <v>28.3</v>
       </c>
       <c r="M50">
         <v>1</v>
@@ -2893,7 +2893,7 @@
         <v>Yes</v>
       </c>
       <c r="O50">
-        <v>77.22</v>
+        <v>56.6</v>
       </c>
       <c r="P50" t="str">
         <v>Y</v>
@@ -2910,7 +2910,7 @@
         <v>Completed</v>
       </c>
       <c r="D51" t="str">
-        <v>26/07/2026</v>
+        <v>12/07/2026</v>
       </c>
       <c r="E51" t="str">
         <v>FYN93N</v>
@@ -2919,10 +2919,10 @@
         <v>Employee - work</v>
       </c>
       <c r="G51">
-        <v>1777</v>
+        <v>2833</v>
       </c>
       <c r="H51">
-        <v>1839</v>
+        <v>2895</v>
       </c>
       <c r="I51" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
@@ -2960,7 +2960,7 @@
         <v>Completed</v>
       </c>
       <c r="D52" t="str">
-        <v>27/07/2026</v>
+        <v>13/07/2026</v>
       </c>
       <c r="E52" t="str">
         <v>FYN93N</v>
@@ -2969,10 +2969,10 @@
         <v>Employee - work</v>
       </c>
       <c r="G52">
-        <v>1839</v>
+        <v>2895</v>
       </c>
       <c r="H52">
-        <v>1916</v>
+        <v>2972</v>
       </c>
       <c r="I52" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
@@ -3010,7 +3010,7 @@
         <v>Completed</v>
       </c>
       <c r="D53" t="str">
-        <v>02/08/2026</v>
+        <v>15/07/2026</v>
       </c>
       <c r="E53" t="str">
         <v>FYN93N</v>
@@ -3019,31 +3019,31 @@
         <v>Employee - work</v>
       </c>
       <c r="G53">
-        <v>1926</v>
+        <v>2972</v>
       </c>
       <c r="H53">
-        <v>1987</v>
+        <v>3011</v>
       </c>
       <c r="I53" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J53" t="str">
-        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K53" t="str">
-        <v>Buying books</v>
+        <v>Attended Parramatta HQ meeting (Leg 1/3)</v>
       </c>
       <c r="L53">
-        <v>30.79</v>
+        <v>38.61</v>
       </c>
       <c r="M53">
         <v>1</v>
       </c>
       <c r="N53" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O53">
-        <v>61.58</v>
+        <v>38.61</v>
       </c>
       <c r="P53" t="str">
         <v>Y</v>
@@ -3060,7 +3060,7 @@
         <v>Completed</v>
       </c>
       <c r="D54" t="str">
-        <v>09/08/2026</v>
+        <v>15/07/2026</v>
       </c>
       <c r="E54" t="str">
         <v>FYN93N</v>
@@ -3069,31 +3069,31 @@
         <v>Employee - work</v>
       </c>
       <c r="G54">
-        <v>2001</v>
+        <v>3011</v>
       </c>
       <c r="H54">
-        <v>2063</v>
+        <v>3033</v>
       </c>
       <c r="I54" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="J54" t="str">
-        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+        <v>Ikea Marsden Park, Hollinsworth, Marsden Park NSW, Australia</v>
       </c>
       <c r="K54" t="str">
-        <v>Buying books</v>
+        <v>Travel from Parramatta HQ to IKEA Marsden Park for office furniture (Leg 2/3)</v>
       </c>
       <c r="L54">
-        <v>30.79</v>
+        <v>22.62</v>
       </c>
       <c r="M54">
         <v>1</v>
       </c>
       <c r="N54" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O54">
-        <v>61.58</v>
+        <v>22.62</v>
       </c>
       <c r="P54" t="str">
         <v>Y</v>
@@ -3110,7 +3110,7 @@
         <v>Completed</v>
       </c>
       <c r="D55" t="str">
-        <v>10/08/2026</v>
+        <v>15/07/2026</v>
       </c>
       <c r="E55" t="str">
         <v>FYN93N</v>
@@ -3119,31 +3119,31 @@
         <v>Employee - work</v>
       </c>
       <c r="G55">
-        <v>2070</v>
+        <v>3033</v>
       </c>
       <c r="H55">
-        <v>2147</v>
+        <v>3062</v>
       </c>
       <c r="I55" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>Ikea Marsden Park, Hollinsworth, Marsden Park NSW, Australia</v>
       </c>
       <c r="J55" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="K55" t="str">
-        <v>Regular Visit to HQ</v>
+        <v>Return from IKEA Marsden Park to Penrith (Leg 3/3)</v>
       </c>
       <c r="L55">
-        <v>38.61</v>
+        <v>28.74</v>
       </c>
       <c r="M55">
         <v>1</v>
       </c>
       <c r="N55" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O55">
-        <v>77.22</v>
+        <v>28.74</v>
       </c>
       <c r="P55" t="str">
         <v>Y</v>
@@ -3160,7 +3160,7 @@
         <v>Completed</v>
       </c>
       <c r="D56" t="str">
-        <v>16/08/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="E56" t="str">
         <v>FYN93N</v>
@@ -3169,34 +3169,34 @@
         <v>Employee - work</v>
       </c>
       <c r="G56">
-        <v>2926</v>
+        <v>3066</v>
       </c>
       <c r="H56">
-        <v>2971</v>
+        <v>3104</v>
       </c>
       <c r="I56" t="str">
-        <v>Edu-Kingdom College Parramatta Sorrell Street Parramatta NSW Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J56" t="str">
-        <v>IKEA Marsden Park Hollinsworth Road Marsden Park NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K56" t="str">
-        <v>To purchase office furniture accessories</v>
+        <v>Attended Parramatta HQ meeting (Leg 1/3)</v>
       </c>
       <c r="L56">
-        <v>22.62</v>
+        <v>38.61</v>
       </c>
       <c r="M56">
         <v>1</v>
       </c>
       <c r="N56" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O56">
-        <v>45.24</v>
+        <v>38.61</v>
       </c>
       <c r="P56" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="57">
@@ -3210,7 +3210,7 @@
         <v>Completed</v>
       </c>
       <c r="D57" t="str">
-        <v>17/08/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="E57" t="str">
         <v>FYN93N</v>
@@ -3219,34 +3219,34 @@
         <v>Employee - work</v>
       </c>
       <c r="G57">
-        <v>2971</v>
+        <v>3104</v>
       </c>
       <c r="H57">
-        <v>3050</v>
+        <v>3127</v>
       </c>
       <c r="I57" t="str">
-        <v>Edu-Kingdom College - Penrith High Street Penrith NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="J57" t="str">
-        <v>KMALL09 LIDCOMBE Shopping Centre Parramatta Road Lidcombe NSW Australia</v>
+        <v>Costco Wholesale Marsden Park, Richmond Road, Marsden Park NSW Australia</v>
       </c>
       <c r="K57" t="str">
-        <v>To purchase office supplies</v>
+        <v>Travel from Parramatta HQ to Costco Marsden Park for bulk supplies (Leg 2/3)</v>
       </c>
       <c r="L57">
-        <v>39.4</v>
+        <v>22.2</v>
       </c>
       <c r="M57">
         <v>1</v>
       </c>
       <c r="N57" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O57">
-        <v>78.8</v>
+        <v>22.2</v>
       </c>
       <c r="P57" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="58">
@@ -3260,7 +3260,7 @@
         <v>Completed</v>
       </c>
       <c r="D58" t="str">
-        <v>19/08/2026</v>
+        <v>17/07/2026</v>
       </c>
       <c r="E58" t="str">
         <v>FYN93N</v>
@@ -3269,34 +3269,34 @@
         <v>Employee - work</v>
       </c>
       <c r="G58">
-        <v>3050</v>
+        <v>3127</v>
       </c>
       <c r="H58">
-        <v>3088</v>
+        <v>3155</v>
       </c>
       <c r="I58" t="str">
-        <v>Edu-Kingdom College - Penrith High Street Penrith NSW Australia</v>
+        <v>Costco Wholesale Marsden Park, Richmond Road, Marsden Park NSW Australia</v>
       </c>
       <c r="J58" t="str">
-        <v>IKEA Marsden Park Hollinsworth Road Marsden Park NSW Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="K58" t="str">
-        <v>To purchase office furniture accessories</v>
+        <v>Return from Costco Marsden Park to Penrith (Leg 3/3)</v>
       </c>
       <c r="L58">
-        <v>18.96</v>
+        <v>27.88</v>
       </c>
       <c r="M58">
         <v>1</v>
       </c>
       <c r="N58" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O58">
-        <v>37.92</v>
+        <v>27.88</v>
       </c>
       <c r="P58" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="59">
@@ -3310,7 +3310,7 @@
         <v>Completed</v>
       </c>
       <c r="D59" t="str">
-        <v>20/08/2026</v>
+        <v>19/07/2026</v>
       </c>
       <c r="E59" t="str">
         <v>FYN93N</v>
@@ -3319,34 +3319,34 @@
         <v>Employee - work</v>
       </c>
       <c r="G59">
-        <v>3088</v>
+        <v>3164</v>
       </c>
       <c r="H59">
-        <v>3164</v>
+        <v>3226</v>
       </c>
       <c r="I59" t="str">
-        <v>Edu-Kingdom College - Penrith High Street Penrith NSW Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J59" t="str">
-        <v>IKEA Marsden Park Hollinsworth Road Marsden Park NSW Australia</v>
+        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
       </c>
       <c r="K59" t="str">
-        <v>Purchase Office furniture</v>
+        <v>Buying books</v>
       </c>
       <c r="L59">
-        <v>18.96</v>
+        <v>30.79</v>
       </c>
       <c r="M59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N59" t="str">
         <v>Yes</v>
       </c>
       <c r="O59">
-        <v>75.84</v>
+        <v>61.58</v>
       </c>
       <c r="P59" t="str">
-        <v>N</v>
+        <v>Y</v>
       </c>
     </row>
     <row r="60">
@@ -3360,7 +3360,7 @@
         <v>Completed</v>
       </c>
       <c r="D60" t="str">
-        <v>23/08/2026</v>
+        <v>20/07/2026</v>
       </c>
       <c r="E60" t="str">
         <v>FYN93N</v>
@@ -3369,22 +3369,22 @@
         <v>Employee - work</v>
       </c>
       <c r="G60">
-        <v>2147</v>
+        <v>3238</v>
       </c>
       <c r="H60">
-        <v>2209</v>
+        <v>3315</v>
       </c>
       <c r="I60" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J60" t="str">
-        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K60" t="str">
-        <v>Buying books</v>
+        <v>Regular Visit to HQ</v>
       </c>
       <c r="L60">
-        <v>30.79</v>
+        <v>38.61</v>
       </c>
       <c r="M60">
         <v>1</v>
@@ -3393,7 +3393,7 @@
         <v>Yes</v>
       </c>
       <c r="O60">
-        <v>61.58</v>
+        <v>77.22</v>
       </c>
       <c r="P60" t="str">
         <v>Y</v>
@@ -3410,7 +3410,7 @@
         <v>Completed</v>
       </c>
       <c r="D61" t="str">
-        <v>24/08/2026</v>
+        <v>21/07/2026</v>
       </c>
       <c r="E61" t="str">
         <v>FYN93N</v>
@@ -3419,10 +3419,10 @@
         <v>Employee - work</v>
       </c>
       <c r="G61">
-        <v>2209</v>
+        <v>3321</v>
       </c>
       <c r="H61">
-        <v>2286</v>
+        <v>3360</v>
       </c>
       <c r="I61" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
@@ -3431,7 +3431,7 @@
         <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K61" t="str">
-        <v>Regular Visit to HQ</v>
+        <v>Attended Parramatta HQ meeting (Leg 1/3)</v>
       </c>
       <c r="L61">
         <v>38.61</v>
@@ -3440,10 +3440,10 @@
         <v>1</v>
       </c>
       <c r="N61" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O61">
-        <v>77.22</v>
+        <v>38.61</v>
       </c>
       <c r="P61" t="str">
         <v>Y</v>
@@ -3460,7 +3460,7 @@
         <v>Completed</v>
       </c>
       <c r="D62" t="str">
-        <v>30/08/2026</v>
+        <v>21/07/2026</v>
       </c>
       <c r="E62" t="str">
         <v>FYN93N</v>
@@ -3469,31 +3469,31 @@
         <v>Employee - work</v>
       </c>
       <c r="G62">
-        <v>2290</v>
+        <v>3360</v>
       </c>
       <c r="H62">
-        <v>2351</v>
+        <v>3371</v>
       </c>
       <c r="I62" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="J62" t="str">
-        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+        <v>KMall09 Lidcombe Shopping Centre, Parramatta Road, Lidcombe NSW, Australia</v>
       </c>
       <c r="K62" t="str">
-        <v>Buying books</v>
+        <v>Travel from Parramatta HQ to KMall09 Lidcombe for educational supplies (Leg 2/3)</v>
       </c>
       <c r="L62">
-        <v>30.79</v>
+        <v>10.82</v>
       </c>
       <c r="M62">
         <v>1</v>
       </c>
       <c r="N62" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O62">
-        <v>61.58</v>
+        <v>10.82</v>
       </c>
       <c r="P62" t="str">
         <v>Y</v>
@@ -3510,7 +3510,7 @@
         <v>Completed</v>
       </c>
       <c r="D63" t="str">
-        <v>31/08/2026</v>
+        <v>21/07/2026</v>
       </c>
       <c r="E63" t="str">
         <v>FYN93N</v>
@@ -3519,31 +3519,31 @@
         <v>Employee - work</v>
       </c>
       <c r="G63">
-        <v>2351</v>
+        <v>3371</v>
       </c>
       <c r="H63">
-        <v>2428</v>
+        <v>3409</v>
       </c>
       <c r="I63" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+        <v>KMall09 Lidcombe Shopping Centre, Parramatta Road, Lidcombe NSW, Australia</v>
       </c>
       <c r="J63" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="K63" t="str">
-        <v>Regular Visit to HQ</v>
+        <v>Return from KMall09 Lidcombe to Penrith (Leg 3/3)</v>
       </c>
       <c r="L63">
-        <v>38.61</v>
+        <v>38.66</v>
       </c>
       <c r="M63">
         <v>1</v>
       </c>
       <c r="N63" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O63">
-        <v>77.22</v>
+        <v>38.66</v>
       </c>
       <c r="P63" t="str">
         <v>Y</v>
@@ -3560,7 +3560,7 @@
         <v>Completed</v>
       </c>
       <c r="D64" t="str">
-        <v>06/09/2026</v>
+        <v>26/07/2026</v>
       </c>
       <c r="E64" t="str">
         <v>FYN93N</v>
@@ -3569,10 +3569,10 @@
         <v>Employee - work</v>
       </c>
       <c r="G64">
-        <v>2428</v>
+        <v>3409</v>
       </c>
       <c r="H64">
-        <v>2490</v>
+        <v>3471</v>
       </c>
       <c r="I64" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
@@ -3610,7 +3610,7 @@
         <v>Completed</v>
       </c>
       <c r="D65" t="str">
-        <v>07/09/2026</v>
+        <v>27/07/2026</v>
       </c>
       <c r="E65" t="str">
         <v>FYN93N</v>
@@ -3619,10 +3619,10 @@
         <v>Employee - work</v>
       </c>
       <c r="G65">
-        <v>2490</v>
+        <v>3477</v>
       </c>
       <c r="H65">
-        <v>2567</v>
+        <v>3554</v>
       </c>
       <c r="I65" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
@@ -3660,7 +3660,7 @@
         <v>Completed</v>
       </c>
       <c r="D66" t="str">
-        <v>13/09/2026</v>
+        <v>29/07/2026</v>
       </c>
       <c r="E66" t="str">
         <v>FYN93N</v>
@@ -3669,31 +3669,31 @@
         <v>Employee - work</v>
       </c>
       <c r="G66">
-        <v>2567</v>
+        <v>3554</v>
       </c>
       <c r="H66">
-        <v>2629</v>
+        <v>3593</v>
       </c>
       <c r="I66" t="str">
         <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
       </c>
       <c r="J66" t="str">
-        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
       </c>
       <c r="K66" t="str">
-        <v>Buying books</v>
+        <v>Attended Parramatta HQ meeting (Leg 1/3)</v>
       </c>
       <c r="L66">
-        <v>30.79</v>
+        <v>38.61</v>
       </c>
       <c r="M66">
         <v>1</v>
       </c>
       <c r="N66" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="O66">
-        <v>61.58</v>
+        <v>38.61</v>
       </c>
       <c r="P66" t="str">
         <v>Y</v>
@@ -3710,48 +3710,2048 @@
         <v>Completed</v>
       </c>
       <c r="D67" t="str">
+        <v>29/07/2026</v>
+      </c>
+      <c r="E67" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F67" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G67">
+        <v>3593</v>
+      </c>
+      <c r="H67">
+        <v>3616</v>
+      </c>
+      <c r="I67" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="J67" t="str">
+        <v>Ikea Marsden Park, Hollinsworth, Marsden Park NSW, Australia</v>
+      </c>
+      <c r="K67" t="str">
+        <v>Travel from Parramatta HQ to IKEA Marsden Park for office furniture (Leg 2/3)</v>
+      </c>
+      <c r="L67">
+        <v>22.62</v>
+      </c>
+      <c r="M67">
+        <v>1</v>
+      </c>
+      <c r="N67" t="str">
+        <v>No</v>
+      </c>
+      <c r="O67">
+        <v>22.62</v>
+      </c>
+      <c r="P67" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B68" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C68" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D68" t="str">
+        <v>29/07/2026</v>
+      </c>
+      <c r="E68" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F68" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G68">
+        <v>3616</v>
+      </c>
+      <c r="H68">
+        <v>3644</v>
+      </c>
+      <c r="I68" t="str">
+        <v>Ikea Marsden Park, Hollinsworth, Marsden Park NSW, Australia</v>
+      </c>
+      <c r="J68" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="K68" t="str">
+        <v>Return from IKEA Marsden Park to Penrith (Leg 3/3)</v>
+      </c>
+      <c r="L68">
+        <v>28.74</v>
+      </c>
+      <c r="M68">
+        <v>1</v>
+      </c>
+      <c r="N68" t="str">
+        <v>No</v>
+      </c>
+      <c r="O68">
+        <v>28.74</v>
+      </c>
+      <c r="P68" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C69" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D69" t="str">
+        <v>31/07/2026</v>
+      </c>
+      <c r="E69" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F69" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G69">
+        <v>3654</v>
+      </c>
+      <c r="H69">
+        <v>3731</v>
+      </c>
+      <c r="I69" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J69" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="K69" t="str">
+        <v>Regular Visit to HQ meeting (Toll-Free route via Great Western Hwy)</v>
+      </c>
+      <c r="L69">
+        <v>38.61</v>
+      </c>
+      <c r="M69">
+        <v>1</v>
+      </c>
+      <c r="N69" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="O69">
+        <v>77.22</v>
+      </c>
+      <c r="P69" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C70" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D70" t="str">
+        <v>31/07/2026</v>
+      </c>
+      <c r="E70" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F70" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G70">
+        <v>3731</v>
+      </c>
+      <c r="H70">
+        <v>3770</v>
+      </c>
+      <c r="I70" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J70" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="K70" t="str">
+        <v>Attended Parramatta HQ meeting (Leg 1/3)</v>
+      </c>
+      <c r="L70">
+        <v>38.61</v>
+      </c>
+      <c r="M70">
+        <v>1</v>
+      </c>
+      <c r="N70" t="str">
+        <v>No</v>
+      </c>
+      <c r="O70">
+        <v>38.61</v>
+      </c>
+      <c r="P70" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C71" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D71" t="str">
+        <v>31/07/2026</v>
+      </c>
+      <c r="E71" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F71" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G71">
+        <v>3770</v>
+      </c>
+      <c r="H71">
+        <v>3792</v>
+      </c>
+      <c r="I71" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="J71" t="str">
+        <v>Ikea Marsden Park, Hollinsworth, Marsden Park NSW, Australia</v>
+      </c>
+      <c r="K71" t="str">
+        <v>Travel from Parramatta HQ to IKEA Marsden Park for office furniture (Leg 2/3)</v>
+      </c>
+      <c r="L71">
+        <v>22.62</v>
+      </c>
+      <c r="M71">
+        <v>1</v>
+      </c>
+      <c r="N71" t="str">
+        <v>No</v>
+      </c>
+      <c r="O71">
+        <v>22.62</v>
+      </c>
+      <c r="P71" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D72" t="str">
+        <v>31/07/2026</v>
+      </c>
+      <c r="E72" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F72" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G72">
+        <v>3792</v>
+      </c>
+      <c r="H72">
+        <v>3821</v>
+      </c>
+      <c r="I72" t="str">
+        <v>Ikea Marsden Park, Hollinsworth, Marsden Park NSW, Australia</v>
+      </c>
+      <c r="J72" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="K72" t="str">
+        <v>Return from IKEA Marsden Park to Penrith (Leg 3/3)</v>
+      </c>
+      <c r="L72">
+        <v>28.74</v>
+      </c>
+      <c r="M72">
+        <v>1</v>
+      </c>
+      <c r="N72" t="str">
+        <v>No</v>
+      </c>
+      <c r="O72">
+        <v>28.74</v>
+      </c>
+      <c r="P72" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D73" t="str">
+        <v>01/08/2026</v>
+      </c>
+      <c r="E73" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F73" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G73">
+        <v>3821</v>
+      </c>
+      <c r="H73">
+        <v>3860</v>
+      </c>
+      <c r="I73" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J73" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="K73" t="str">
+        <v>Attended Parramatta HQ meeting (Leg 1/3)</v>
+      </c>
+      <c r="L73">
+        <v>38.61</v>
+      </c>
+      <c r="M73">
+        <v>1</v>
+      </c>
+      <c r="N73" t="str">
+        <v>No</v>
+      </c>
+      <c r="O73">
+        <v>38.61</v>
+      </c>
+      <c r="P73" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C74" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D74" t="str">
+        <v>01/08/2026</v>
+      </c>
+      <c r="E74" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F74" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G74">
+        <v>3860</v>
+      </c>
+      <c r="H74">
+        <v>3871</v>
+      </c>
+      <c r="I74" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="J74" t="str">
+        <v>KMall09 Lidcombe Shopping Centre, Parramatta Road, Lidcombe NSW, Australia</v>
+      </c>
+      <c r="K74" t="str">
+        <v>Travel from Parramatta HQ to KMall09 Lidcombe for educational supplies (Leg 2/3)</v>
+      </c>
+      <c r="L74">
+        <v>10.82</v>
+      </c>
+      <c r="M74">
+        <v>1</v>
+      </c>
+      <c r="N74" t="str">
+        <v>No</v>
+      </c>
+      <c r="O74">
+        <v>10.82</v>
+      </c>
+      <c r="P74" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C75" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D75" t="str">
+        <v>01/08/2026</v>
+      </c>
+      <c r="E75" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F75" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G75">
+        <v>3871</v>
+      </c>
+      <c r="H75">
+        <v>3909</v>
+      </c>
+      <c r="I75" t="str">
+        <v>KMall09 Lidcombe Shopping Centre, Parramatta Road, Lidcombe NSW, Australia</v>
+      </c>
+      <c r="J75" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="K75" t="str">
+        <v>Return from KMall09 Lidcombe to Penrith (Leg 3/3)</v>
+      </c>
+      <c r="L75">
+        <v>38.66</v>
+      </c>
+      <c r="M75">
+        <v>1</v>
+      </c>
+      <c r="N75" t="str">
+        <v>No</v>
+      </c>
+      <c r="O75">
+        <v>38.66</v>
+      </c>
+      <c r="P75" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C76" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D76" t="str">
+        <v>02/08/2026</v>
+      </c>
+      <c r="E76" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F76" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G76">
+        <v>3909</v>
+      </c>
+      <c r="H76">
+        <v>3971</v>
+      </c>
+      <c r="I76" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J76" t="str">
+        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+      </c>
+      <c r="K76" t="str">
+        <v>Buying books</v>
+      </c>
+      <c r="L76">
+        <v>30.79</v>
+      </c>
+      <c r="M76">
+        <v>1</v>
+      </c>
+      <c r="N76" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="O76">
+        <v>61.58</v>
+      </c>
+      <c r="P76" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C77" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D77" t="str">
+        <v>07/08/2026</v>
+      </c>
+      <c r="E77" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F77" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G77">
+        <v>3979</v>
+      </c>
+      <c r="H77">
+        <v>4035</v>
+      </c>
+      <c r="I77" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J77" t="str">
+        <v>Costco Wholesale Marsden Park, Richmond Road, Marsden Park NSW Australia</v>
+      </c>
+      <c r="K77" t="str">
+        <v>Purchase bulk office and student supplies (Toll-Free via Richmond Rd)</v>
+      </c>
+      <c r="L77">
+        <v>27.88</v>
+      </c>
+      <c r="M77">
+        <v>1</v>
+      </c>
+      <c r="N77" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="O77">
+        <v>55.76</v>
+      </c>
+      <c r="P77" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C78" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D78" t="str">
+        <v>09/08/2026</v>
+      </c>
+      <c r="E78" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F78" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G78">
+        <v>4035</v>
+      </c>
+      <c r="H78">
+        <v>4096</v>
+      </c>
+      <c r="I78" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J78" t="str">
+        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+      </c>
+      <c r="K78" t="str">
+        <v>Buying books</v>
+      </c>
+      <c r="L78">
+        <v>30.79</v>
+      </c>
+      <c r="M78">
+        <v>1</v>
+      </c>
+      <c r="N78" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="O78">
+        <v>61.58</v>
+      </c>
+      <c r="P78" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D79" t="str">
+        <v>10/08/2026</v>
+      </c>
+      <c r="E79" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F79" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G79">
+        <v>4103</v>
+      </c>
+      <c r="H79">
+        <v>4180</v>
+      </c>
+      <c r="I79" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J79" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="K79" t="str">
+        <v>Regular Visit to HQ</v>
+      </c>
+      <c r="L79">
+        <v>38.61</v>
+      </c>
+      <c r="M79">
+        <v>1</v>
+      </c>
+      <c r="N79" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="O79">
+        <v>77.22</v>
+      </c>
+      <c r="P79" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C80" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D80" t="str">
+        <v>11/08/2026</v>
+      </c>
+      <c r="E80" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F80" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G80">
+        <v>4180</v>
+      </c>
+      <c r="H80">
+        <v>4258</v>
+      </c>
+      <c r="I80" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J80" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="K80" t="str">
+        <v>Regular Visit to HQ meeting (Toll-Free route via Great Western Hwy)</v>
+      </c>
+      <c r="L80">
+        <v>38.61</v>
+      </c>
+      <c r="M80">
+        <v>1</v>
+      </c>
+      <c r="N80" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="O80">
+        <v>77.22</v>
+      </c>
+      <c r="P80" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C81" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D81" t="str">
+        <v>14/08/2026</v>
+      </c>
+      <c r="E81" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F81" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G81">
+        <v>4265</v>
+      </c>
+      <c r="H81">
+        <v>4303</v>
+      </c>
+      <c r="I81" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J81" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="K81" t="str">
+        <v>Attended Parramatta HQ meeting (Leg 1/3)</v>
+      </c>
+      <c r="L81">
+        <v>38.61</v>
+      </c>
+      <c r="M81">
+        <v>1</v>
+      </c>
+      <c r="N81" t="str">
+        <v>No</v>
+      </c>
+      <c r="O81">
+        <v>38.61</v>
+      </c>
+      <c r="P81" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D82" t="str">
+        <v>14/08/2026</v>
+      </c>
+      <c r="E82" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F82" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G82">
+        <v>4303</v>
+      </c>
+      <c r="H82">
+        <v>4325</v>
+      </c>
+      <c r="I82" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="J82" t="str">
+        <v>Costco Wholesale Marsden Park, Richmond Road, Marsden Park NSW Australia</v>
+      </c>
+      <c r="K82" t="str">
+        <v>Travel from Parramatta HQ to Costco Marsden Park for bulk supplies (Leg 2/3)</v>
+      </c>
+      <c r="L82">
+        <v>22.2</v>
+      </c>
+      <c r="M82">
+        <v>1</v>
+      </c>
+      <c r="N82" t="str">
+        <v>No</v>
+      </c>
+      <c r="O82">
+        <v>22.2</v>
+      </c>
+      <c r="P82" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D83" t="str">
+        <v>14/08/2026</v>
+      </c>
+      <c r="E83" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F83" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G83">
+        <v>4325</v>
+      </c>
+      <c r="H83">
+        <v>4353</v>
+      </c>
+      <c r="I83" t="str">
+        <v>Costco Wholesale Marsden Park, Richmond Road, Marsden Park NSW Australia</v>
+      </c>
+      <c r="J83" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="K83" t="str">
+        <v>Return from Costco Marsden Park to Penrith (Leg 3/3)</v>
+      </c>
+      <c r="L83">
+        <v>27.88</v>
+      </c>
+      <c r="M83">
+        <v>1</v>
+      </c>
+      <c r="N83" t="str">
+        <v>No</v>
+      </c>
+      <c r="O83">
+        <v>27.88</v>
+      </c>
+      <c r="P83" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C84" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D84" t="str">
+        <v>16/08/2026</v>
+      </c>
+      <c r="E84" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G84">
+        <v>4357</v>
+      </c>
+      <c r="H84">
+        <v>4419</v>
+      </c>
+      <c r="I84" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J84" t="str">
+        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+      </c>
+      <c r="K84" t="str">
+        <v>Buying books</v>
+      </c>
+      <c r="L84">
+        <v>30.79</v>
+      </c>
+      <c r="M84">
+        <v>1</v>
+      </c>
+      <c r="N84" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="O84">
+        <v>61.58</v>
+      </c>
+      <c r="P84" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C85" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D85" t="str">
+        <v>17/08/2026</v>
+      </c>
+      <c r="E85" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F85" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G85">
+        <v>4424</v>
+      </c>
+      <c r="H85">
+        <v>4502</v>
+      </c>
+      <c r="I85" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J85" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="K85" t="str">
+        <v>Regular Visit to HQ</v>
+      </c>
+      <c r="L85">
+        <v>38.61</v>
+      </c>
+      <c r="M85">
+        <v>1</v>
+      </c>
+      <c r="N85" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="O85">
+        <v>77.22</v>
+      </c>
+      <c r="P85" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C86" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D86" t="str">
+        <v>23/08/2026</v>
+      </c>
+      <c r="E86" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F86" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G86">
+        <v>4511</v>
+      </c>
+      <c r="H86">
+        <v>4573</v>
+      </c>
+      <c r="I86" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J86" t="str">
+        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+      </c>
+      <c r="K86" t="str">
+        <v>Buying books</v>
+      </c>
+      <c r="L86">
+        <v>30.79</v>
+      </c>
+      <c r="M86">
+        <v>1</v>
+      </c>
+      <c r="N86" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="O86">
+        <v>61.58</v>
+      </c>
+      <c r="P86" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B87" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C87" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D87" t="str">
+        <v>24/08/2026</v>
+      </c>
+      <c r="E87" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F87" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G87">
+        <v>4584</v>
+      </c>
+      <c r="H87">
+        <v>4661</v>
+      </c>
+      <c r="I87" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J87" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="K87" t="str">
+        <v>Regular Visit to HQ</v>
+      </c>
+      <c r="L87">
+        <v>38.61</v>
+      </c>
+      <c r="M87">
+        <v>1</v>
+      </c>
+      <c r="N87" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="O87">
+        <v>77.22</v>
+      </c>
+      <c r="P87" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C88" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D88" t="str">
+        <v>26/08/2026</v>
+      </c>
+      <c r="E88" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F88" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G88">
+        <v>4666</v>
+      </c>
+      <c r="H88">
+        <v>4705</v>
+      </c>
+      <c r="I88" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J88" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="K88" t="str">
+        <v>Attended Parramatta HQ meeting (Leg 1/3)</v>
+      </c>
+      <c r="L88">
+        <v>38.61</v>
+      </c>
+      <c r="M88">
+        <v>1</v>
+      </c>
+      <c r="N88" t="str">
+        <v>No</v>
+      </c>
+      <c r="O88">
+        <v>38.61</v>
+      </c>
+      <c r="P88" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C89" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D89" t="str">
+        <v>26/08/2026</v>
+      </c>
+      <c r="E89" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F89" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G89">
+        <v>4705</v>
+      </c>
+      <c r="H89">
+        <v>4716</v>
+      </c>
+      <c r="I89" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="J89" t="str">
+        <v>KMall09 Lidcombe Shopping Centre, Parramatta Road, Lidcombe NSW, Australia</v>
+      </c>
+      <c r="K89" t="str">
+        <v>Travel from Parramatta HQ to KMall09 Lidcombe for educational supplies (Leg 2/3)</v>
+      </c>
+      <c r="L89">
+        <v>10.82</v>
+      </c>
+      <c r="M89">
+        <v>1</v>
+      </c>
+      <c r="N89" t="str">
+        <v>No</v>
+      </c>
+      <c r="O89">
+        <v>10.82</v>
+      </c>
+      <c r="P89" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C90" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D90" t="str">
+        <v>26/08/2026</v>
+      </c>
+      <c r="E90" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F90" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G90">
+        <v>4716</v>
+      </c>
+      <c r="H90">
+        <v>4754</v>
+      </c>
+      <c r="I90" t="str">
+        <v>KMall09 Lidcombe Shopping Centre, Parramatta Road, Lidcombe NSW, Australia</v>
+      </c>
+      <c r="J90" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="K90" t="str">
+        <v>Return from KMall09 Lidcombe to Penrith (Leg 3/3)</v>
+      </c>
+      <c r="L90">
+        <v>38.66</v>
+      </c>
+      <c r="M90">
+        <v>1</v>
+      </c>
+      <c r="N90" t="str">
+        <v>No</v>
+      </c>
+      <c r="O90">
+        <v>38.66</v>
+      </c>
+      <c r="P90" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C91" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D91" t="str">
+        <v>27/08/2026</v>
+      </c>
+      <c r="E91" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F91" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G91">
+        <v>4761</v>
+      </c>
+      <c r="H91">
+        <v>4800</v>
+      </c>
+      <c r="I91" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J91" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="K91" t="str">
+        <v>Attended Parramatta HQ meeting (Leg 1/3)</v>
+      </c>
+      <c r="L91">
+        <v>38.61</v>
+      </c>
+      <c r="M91">
+        <v>1</v>
+      </c>
+      <c r="N91" t="str">
+        <v>No</v>
+      </c>
+      <c r="O91">
+        <v>38.61</v>
+      </c>
+      <c r="P91" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C92" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D92" t="str">
+        <v>27/08/2026</v>
+      </c>
+      <c r="E92" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F92" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G92">
+        <v>4800</v>
+      </c>
+      <c r="H92">
+        <v>4811</v>
+      </c>
+      <c r="I92" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="J92" t="str">
+        <v>KMall09 Lidcombe Shopping Centre, Parramatta Road, Lidcombe NSW, Australia</v>
+      </c>
+      <c r="K92" t="str">
+        <v>Travel from Parramatta HQ to KMall09 Lidcombe for educational supplies (Leg 2/3)</v>
+      </c>
+      <c r="L92">
+        <v>10.82</v>
+      </c>
+      <c r="M92">
+        <v>1</v>
+      </c>
+      <c r="N92" t="str">
+        <v>No</v>
+      </c>
+      <c r="O92">
+        <v>10.82</v>
+      </c>
+      <c r="P92" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C93" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D93" t="str">
+        <v>27/08/2026</v>
+      </c>
+      <c r="E93" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F93" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G93">
+        <v>4811</v>
+      </c>
+      <c r="H93">
+        <v>4849</v>
+      </c>
+      <c r="I93" t="str">
+        <v>KMall09 Lidcombe Shopping Centre, Parramatta Road, Lidcombe NSW, Australia</v>
+      </c>
+      <c r="J93" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="K93" t="str">
+        <v>Return from KMall09 Lidcombe to Penrith (Leg 3/3)</v>
+      </c>
+      <c r="L93">
+        <v>38.66</v>
+      </c>
+      <c r="M93">
+        <v>1</v>
+      </c>
+      <c r="N93" t="str">
+        <v>No</v>
+      </c>
+      <c r="O93">
+        <v>38.66</v>
+      </c>
+      <c r="P93" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C94" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D94" t="str">
+        <v>30/08/2026</v>
+      </c>
+      <c r="E94" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F94" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G94">
+        <v>4849</v>
+      </c>
+      <c r="H94">
+        <v>4911</v>
+      </c>
+      <c r="I94" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J94" t="str">
+        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+      </c>
+      <c r="K94" t="str">
+        <v>Buying books</v>
+      </c>
+      <c r="L94">
+        <v>30.79</v>
+      </c>
+      <c r="M94">
+        <v>1</v>
+      </c>
+      <c r="N94" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="O94">
+        <v>61.58</v>
+      </c>
+      <c r="P94" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C95" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D95" t="str">
+        <v>31/08/2026</v>
+      </c>
+      <c r="E95" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F95" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G95">
+        <v>4911</v>
+      </c>
+      <c r="H95">
+        <v>4988</v>
+      </c>
+      <c r="I95" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J95" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="K95" t="str">
+        <v>Regular Visit to HQ</v>
+      </c>
+      <c r="L95">
+        <v>38.61</v>
+      </c>
+      <c r="M95">
+        <v>1</v>
+      </c>
+      <c r="N95" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="O95">
+        <v>77.22</v>
+      </c>
+      <c r="P95" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B96" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C96" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D96" t="str">
+        <v>01/09/2026</v>
+      </c>
+      <c r="E96" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F96" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G96">
+        <v>4988</v>
+      </c>
+      <c r="H96">
+        <v>5062</v>
+      </c>
+      <c r="I96" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J96" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="K96" t="str">
+        <v>Urgent executive meeting at HQ (via M4 Motorway)</v>
+      </c>
+      <c r="L96">
+        <v>36.8</v>
+      </c>
+      <c r="M96">
+        <v>1</v>
+      </c>
+      <c r="N96" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="O96">
+        <v>73.6</v>
+      </c>
+      <c r="P96" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C97" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D97" t="str">
+        <v>02/09/2026</v>
+      </c>
+      <c r="E97" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F97" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G97">
+        <v>5062</v>
+      </c>
+      <c r="H97">
+        <v>5135</v>
+      </c>
+      <c r="I97" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J97" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="K97" t="str">
+        <v>Urgent executive meeting at HQ (via M4 Motorway)</v>
+      </c>
+      <c r="L97">
+        <v>36.8</v>
+      </c>
+      <c r="M97">
+        <v>1</v>
+      </c>
+      <c r="N97" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="O97">
+        <v>73.6</v>
+      </c>
+      <c r="P97" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B98" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C98" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D98" t="str">
+        <v>04/09/2026</v>
+      </c>
+      <c r="E98" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F98" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G98">
+        <v>5135</v>
+      </c>
+      <c r="H98">
+        <v>5174</v>
+      </c>
+      <c r="I98" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J98" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="K98" t="str">
+        <v>Attended Parramatta HQ meeting (Leg 1/3)</v>
+      </c>
+      <c r="L98">
+        <v>38.61</v>
+      </c>
+      <c r="M98">
+        <v>1</v>
+      </c>
+      <c r="N98" t="str">
+        <v>No</v>
+      </c>
+      <c r="O98">
+        <v>38.61</v>
+      </c>
+      <c r="P98" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C99" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D99" t="str">
+        <v>04/09/2026</v>
+      </c>
+      <c r="E99" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F99" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G99">
+        <v>5174</v>
+      </c>
+      <c r="H99">
+        <v>5196</v>
+      </c>
+      <c r="I99" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="J99" t="str">
+        <v>Costco Wholesale Marsden Park, Richmond Road, Marsden Park NSW Australia</v>
+      </c>
+      <c r="K99" t="str">
+        <v>Travel from Parramatta HQ to Costco Marsden Park for bulk supplies (Leg 2/3)</v>
+      </c>
+      <c r="L99">
+        <v>22.2</v>
+      </c>
+      <c r="M99">
+        <v>1</v>
+      </c>
+      <c r="N99" t="str">
+        <v>No</v>
+      </c>
+      <c r="O99">
+        <v>22.2</v>
+      </c>
+      <c r="P99" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C100" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D100" t="str">
+        <v>04/09/2026</v>
+      </c>
+      <c r="E100" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F100" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G100">
+        <v>5196</v>
+      </c>
+      <c r="H100">
+        <v>5224</v>
+      </c>
+      <c r="I100" t="str">
+        <v>Costco Wholesale Marsden Park, Richmond Road, Marsden Park NSW Australia</v>
+      </c>
+      <c r="J100" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="K100" t="str">
+        <v>Return from Costco Marsden Park to Penrith (Leg 3/3)</v>
+      </c>
+      <c r="L100">
+        <v>27.88</v>
+      </c>
+      <c r="M100">
+        <v>1</v>
+      </c>
+      <c r="N100" t="str">
+        <v>No</v>
+      </c>
+      <c r="O100">
+        <v>27.88</v>
+      </c>
+      <c r="P100" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C101" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D101" t="str">
+        <v>06/09/2026</v>
+      </c>
+      <c r="E101" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F101" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G101">
+        <v>5224</v>
+      </c>
+      <c r="H101">
+        <v>5286</v>
+      </c>
+      <c r="I101" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J101" t="str">
+        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+      </c>
+      <c r="K101" t="str">
+        <v>Buying books</v>
+      </c>
+      <c r="L101">
+        <v>30.79</v>
+      </c>
+      <c r="M101">
+        <v>1</v>
+      </c>
+      <c r="N101" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="O101">
+        <v>61.58</v>
+      </c>
+      <c r="P101" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D102" t="str">
+        <v>07/09/2026</v>
+      </c>
+      <c r="E102" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F102" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G102">
+        <v>5286</v>
+      </c>
+      <c r="H102">
+        <v>5363</v>
+      </c>
+      <c r="I102" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J102" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="K102" t="str">
+        <v>Regular Visit to HQ</v>
+      </c>
+      <c r="L102">
+        <v>38.61</v>
+      </c>
+      <c r="M102">
+        <v>1</v>
+      </c>
+      <c r="N102" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="O102">
+        <v>77.22</v>
+      </c>
+      <c r="P102" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D103" t="str">
+        <v>10/09/2026</v>
+      </c>
+      <c r="E103" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F103" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G103">
+        <v>5363</v>
+      </c>
+      <c r="H103">
+        <v>5401</v>
+      </c>
+      <c r="I103" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J103" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="K103" t="str">
+        <v>Attended Parramatta HQ meeting (Leg 1/3)</v>
+      </c>
+      <c r="L103">
+        <v>38.61</v>
+      </c>
+      <c r="M103">
+        <v>1</v>
+      </c>
+      <c r="N103" t="str">
+        <v>No</v>
+      </c>
+      <c r="O103">
+        <v>38.61</v>
+      </c>
+      <c r="P103" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C104" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D104" t="str">
+        <v>10/09/2026</v>
+      </c>
+      <c r="E104" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F104" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G104">
+        <v>5401</v>
+      </c>
+      <c r="H104">
+        <v>5424</v>
+      </c>
+      <c r="I104" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="J104" t="str">
+        <v>Ikea Marsden Park, Hollinsworth, Marsden Park NSW, Australia</v>
+      </c>
+      <c r="K104" t="str">
+        <v>Travel from Parramatta HQ to IKEA Marsden Park for office furniture (Leg 2/3)</v>
+      </c>
+      <c r="L104">
+        <v>22.62</v>
+      </c>
+      <c r="M104">
+        <v>1</v>
+      </c>
+      <c r="N104" t="str">
+        <v>No</v>
+      </c>
+      <c r="O104">
+        <v>22.62</v>
+      </c>
+      <c r="P104" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B105" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C105" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D105" t="str">
+        <v>10/09/2026</v>
+      </c>
+      <c r="E105" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F105" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G105">
+        <v>5424</v>
+      </c>
+      <c r="H105">
+        <v>5453</v>
+      </c>
+      <c r="I105" t="str">
+        <v>Ikea Marsden Park, Hollinsworth, Marsden Park NSW, Australia</v>
+      </c>
+      <c r="J105" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="K105" t="str">
+        <v>Return from IKEA Marsden Park to Penrith (Leg 3/3)</v>
+      </c>
+      <c r="L105">
+        <v>28.74</v>
+      </c>
+      <c r="M105">
+        <v>1</v>
+      </c>
+      <c r="N105" t="str">
+        <v>No</v>
+      </c>
+      <c r="O105">
+        <v>28.74</v>
+      </c>
+      <c r="P105" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C106" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D106" t="str">
+        <v>13/09/2026</v>
+      </c>
+      <c r="E106" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F106" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G106">
+        <v>5453</v>
+      </c>
+      <c r="H106">
+        <v>5514</v>
+      </c>
+      <c r="I106" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J106" t="str">
+        <v>Five Senses Education Prospect Highway Seven Hills NSW Australia</v>
+      </c>
+      <c r="K106" t="str">
+        <v>Buying books</v>
+      </c>
+      <c r="L106">
+        <v>30.79</v>
+      </c>
+      <c r="M106">
+        <v>1</v>
+      </c>
+      <c r="N106" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="O106">
+        <v>61.58</v>
+      </c>
+      <c r="P106" t="str">
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>Not uploaded</v>
+      </c>
+      <c r="B107" t="str">
+        <v>Employee</v>
+      </c>
+      <c r="C107" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="D107" t="str">
         <v>14/09/2026</v>
       </c>
-      <c r="E67" t="str">
-        <v>FYN93N</v>
-      </c>
-      <c r="F67" t="str">
-        <v>Employee - work</v>
-      </c>
-      <c r="G67">
-        <v>2637</v>
-      </c>
-      <c r="H67">
-        <v>2714</v>
-      </c>
-      <c r="I67" t="str">
-        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
-      </c>
-      <c r="J67" t="str">
-        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
-      </c>
-      <c r="K67" t="str">
+      <c r="E107" t="str">
+        <v>FYN93N</v>
+      </c>
+      <c r="F107" t="str">
+        <v>Employee - work</v>
+      </c>
+      <c r="G107">
+        <v>5514</v>
+      </c>
+      <c r="H107">
+        <v>5592</v>
+      </c>
+      <c r="I107" t="str">
+        <v>Edu-Kingdom College High Street Penrith NSW Australia</v>
+      </c>
+      <c r="J107" t="str">
+        <v>Edu-Kingdom College Sorrell Street Parramatta NSW Australia</v>
+      </c>
+      <c r="K107" t="str">
         <v>Regular Visit to HQ</v>
       </c>
-      <c r="L67">
-        <v>38.61</v>
-      </c>
-      <c r="M67">
-        <v>1</v>
-      </c>
-      <c r="N67" t="str">
+      <c r="L107">
+        <v>38.61</v>
+      </c>
+      <c r="M107">
+        <v>1</v>
+      </c>
+      <c r="N107" t="str">
         <v>Yes</v>
       </c>
-      <c r="O67">
+      <c r="O107">
         <v>77.22</v>
       </c>
-      <c r="P67" t="str">
+      <c r="P107" t="str">
         <v>Y</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P67"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P107"/>
   </ignoredErrors>
 </worksheet>
 </file>